--- a/dataset/bd_cobranca.xlsx
+++ b/dataset/bd_cobranca.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,32 +46,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001D9E75"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="001A1530"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
@@ -83,7 +57,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -102,26 +76,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001D9E75"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDE8FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C0392B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -145,20 +104,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00C8C0F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C8C0F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C8C0F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C8C0F0"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="00C0392B"/>
       </left>
       <right style="thin">
@@ -175,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,46 +131,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -593,22 +505,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -621,7 +534,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 22/06/2026  ·  Total de registros: 4</t>
+          <t>Gerado em: 23/06/2026  ·  Total de registros: 0</t>
         </is>
       </c>
     </row>
@@ -629,310 +542,87 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Data Cobrança</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Data Vencimento</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Data Pagamento</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>CNPJ</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Data Produção</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Fornecedor</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Qtd</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Remonte / Defeito</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Real Cortado</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Min. Gerados</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>62.470.324/0001-40</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Pago</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>300258637</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>M K INDUSTRIA TEXTIL LTDA</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>ESGARÇANDO</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>798</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>201.64</v>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>235.9188</v>
+          <t>TOTAL HISTÓRICO</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>62.470.324/0001-40</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Pago</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>300258637</v>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>M K INDUSTRIA TEXTIL LTDA</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>PONTO ESTOURADO</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>798</v>
-      </c>
-      <c r="L6" s="10" t="n">
-        <v>11.47</v>
-      </c>
-      <c r="M6" s="14" t="n">
-        <v>13.4199</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>62.470.324/0001-40</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Pago</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>300258637</v>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>M K INDUSTRIA TEXTIL LTDA</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>SEM ARREMATE</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>798</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="M7" s="9" t="n">
-        <v>2.7027</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>62.470.324/0001-40</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Pago</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>300258637</v>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>M K INDUSTRIA TEXTIL LTDA</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>ESGARÇANDO</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>798</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>211.47</v>
-      </c>
-      <c r="M8" s="14" t="n">
-        <v>247.4199</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL HISTÓRICO</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="n">
-        <v>499.4613000000001</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Documento gerado automaticamente pelo sistema de Controle de Qualidade. Este histórico acumula todas as cobranças confirmadas no período.</t>
         </is>
@@ -940,10 +630,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dataset/bd_cobranca.xlsx
+++ b/dataset/bd_cobranca.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,38 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="00534AB7"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001D9E75"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A1530"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A1530"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
@@ -57,7 +89,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,11 +108,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF9F27"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C0392B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -104,6 +151,20 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="00C8C0F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C8C0F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C8C0F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C8C0F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="00C0392B"/>
       </left>
       <right style="thin">
@@ -120,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -131,13 +192,52 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -505,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,7 +634,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em: 23/06/2026  ·  Total de registros: 0</t>
+          <t>Gerado em: 23/06/2026  ·  Total de registros: 49</t>
         </is>
       </c>
     </row>
@@ -611,18 +711,2860 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
+    <row r="5" ht="17" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>PAG-C4F52E15</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>30.913.713/0002-98</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>300265766</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>J M CONFECCOES &amp; CIA LTDA FILIAL</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1073</v>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1086</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>354.09</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>414.2853</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="N6" s="16" t="n">
+        <v>31.824</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>ESGARÇANDO</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>398.7359999999999</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>TROCAR</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="N8" s="16" t="n">
+        <v>6.107399999999999</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>3.0888</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="N10" s="16" t="n">
+        <v>11.1969</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>22.8501</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr"/>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N12" s="16" t="n">
+        <v>14.976</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>5.265</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="N14" s="16" t="n">
+        <v>17.4096</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>29.016</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N16" s="16" t="n">
+        <v>3.8259</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>ESGARÇANDO</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>33.22799999999999</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr"/>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="N18" s="16" t="n">
+        <v>5.4405</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>300259168</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1428</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>14.04</v>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr"/>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="N20" s="16" t="n">
+        <v>1.0881</v>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>ESGARÇANDO</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>3.3228</v>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr"/>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N22" s="16" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>0.7253999999999999</v>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr"/>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N24" s="16" t="n">
+        <v>0.8072999999999999</v>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>ESGARÇANDO</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>3.3228</v>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr"/>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>ESGARÇANDO</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="N26" s="16" t="n">
+        <v>13.0221</v>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>1.2753</v>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr"/>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>300256868</v>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>768</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N28" s="16" t="n">
+        <v>1.755</v>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>300256868</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>768</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>0.8072999999999999</v>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr"/>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>300256868</v>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>768</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N30" s="16" t="n">
+        <v>0.3861</v>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>300256868</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>768</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N31" s="10" t="n">
+        <v>1.872</v>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr"/>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>300256868</v>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" s="15" t="inlineStr">
+        <is>
+          <t>ESGARÇANDO</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>768</v>
+      </c>
+      <c r="M32" s="12" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="N32" s="16" t="n">
+        <v>19.9368</v>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>300256868</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>768</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v>1.0881</v>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr"/>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>300256868</v>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>768</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N34" s="16" t="n">
+        <v>3.4398</v>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>300256868</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>768</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N35" s="10" t="n">
+        <v>4.247100000000001</v>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr"/>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>300256868</v>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="15" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>768</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N36" s="16" t="n">
+        <v>0.3861</v>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>300256868</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>768</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="N37" s="10" t="n">
+        <v>2.2932</v>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr"/>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="N38" s="16" t="n">
+        <v>4.586399999999999</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N39" s="10" t="n">
+        <v>2.3166</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr"/>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N40" s="16" t="n">
+        <v>4.387499999999999</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N41" s="10" t="n">
+        <v>3.744</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr"/>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K42" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>6.540000000000001</v>
+      </c>
+      <c r="N42" s="16" t="n">
+        <v>7.651800000000001</v>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="N43" s="10" t="n">
+        <v>4.7151</v>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>300263683</v>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" s="15" t="inlineStr">
+        <is>
+          <t>ESGARÇANDO</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M44" s="12" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="N44" s="16" t="n">
+        <v>9.968399999999999</v>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>300263689</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>403</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="N45" s="10" t="n">
+        <v>1.9305</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr"/>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>300263689</v>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>403</v>
+      </c>
+      <c r="M46" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N46" s="16" t="n">
+        <v>1.755</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>300263689</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>403</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N47" s="10" t="n">
+        <v>1.2753</v>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr"/>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>300263689</v>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L48" s="12" t="n">
+        <v>403</v>
+      </c>
+      <c r="M48" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N48" s="16" t="n">
+        <v>0.3627</v>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>300263689</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>ESGARÇANDO</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>403</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="N49" s="10" t="n">
+        <v>29.9052</v>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr"/>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="n">
+        <v>300263689</v>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K50" s="15" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>403</v>
+      </c>
+      <c r="M50" s="12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N50" s="16" t="n">
+        <v>2.7027</v>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>300264848</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>TROCAR</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>1520</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="N51" s="10" t="n">
+        <v>2.0358</v>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr"/>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="n">
+        <v>300264848</v>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="15" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>1520</v>
+      </c>
+      <c r="M52" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N52" s="16" t="n">
+        <v>0.3627</v>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>PAG-889E9071</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>60.364.294/0002-43</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>300264848</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>FIOS DO SERTÃO LTDA</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>1520</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N53" s="10" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
           <t>TOTAL HISTÓRICO</t>
         </is>
       </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="N54" s="18" t="n">
+        <v>1150.5195</v>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>Documento gerado automaticamente pelo sistema de Controle de Qualidade. Este histórico acumula todas as cobranças confirmadas no período.</t>
         </is>
@@ -630,9 +3572,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A56:N56"/>
+    <mergeCell ref="A54:M54"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A5:M5"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
